--- a/data/trans_dic/P36$otros-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P36$otros-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que desayuna, otros alimentos</t>
+          <t>Población que desayuna, otros alimentos (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,44</t>
+          <t>0,4; 2,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,8</t>
+          <t>0,2; 1,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,72; 7,07</t>
+          <t>2,88; 7,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,65</t>
+          <t>0,29; 3,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,27; 5,41</t>
+          <t>1,08; 5,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,23; 8,48</t>
+          <t>3,27; 8,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,09</t>
+          <t>0,43; 2,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,74</t>
+          <t>0,69; 2,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,54; 6,8</t>
+          <t>3,56; 6,79</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,31; 5,1</t>
+          <t>1,23; 5,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,23</t>
+          <t>0,24; 2,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,19; 6,78</t>
+          <t>2,18; 6,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,21</t>
+          <t>0,63; 3,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,3</t>
+          <t>0,0; 2,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,62; 5,97</t>
+          <t>1,51; 5,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,31</t>
+          <t>1,23; 3,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,94</t>
+          <t>0,37; 1,97</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,35; 5,31</t>
+          <t>2,4; 5,33</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,28</t>
+          <t>0,93; 3,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,54</t>
+          <t>0,56; 2,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,68; 6,25</t>
+          <t>2,67; 6,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,86</t>
+          <t>0,0; 3,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,62</t>
+          <t>0,38; 3,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 6,69</t>
+          <t>0,6; 6,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,8</t>
+          <t>0,85; 2,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,25</t>
+          <t>0,72; 2,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,54; 5,54</t>
+          <t>2,5; 5,53</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,97</t>
+          <t>1,29; 3,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,36</t>
+          <t>0,71; 2,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,54; 6,09</t>
+          <t>3,61; 6,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,35</t>
+          <t>1,15; 3,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,3</t>
+          <t>0,6; 2,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,14; 4,6</t>
+          <t>2,19; 4,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,49; 2,73</t>
+          <t>1,46; 2,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,04</t>
+          <t>0,79; 2,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,32; 5,15</t>
+          <t>3,25; 5,1</t>
         </is>
       </c>
     </row>
@@ -1118,32 +1118,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 4,09</t>
+          <t>0,74; 4,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,87</t>
+          <t>0,19; 1,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,61; 4,39</t>
+          <t>1,7; 4,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,09</t>
+          <t>0,43; 1,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,69</t>
+          <t>0,29; 1,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,24; 7,97</t>
+          <t>4,4; 7,82</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1153,12 +1153,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,53</t>
+          <t>0,41; 1,48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,42; 5,72</t>
+          <t>3,41; 5,67</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,03</t>
+          <t>0,33; 2,78</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,56</t>
+          <t>0,0; 2,55</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,19; 5,65</t>
+          <t>1,15; 5,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,37; 2,95</t>
+          <t>1,38; 2,95</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,58</t>
+          <t>0,37; 1,52</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,66; 5,02</t>
+          <t>2,83; 5,3</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,63</t>
+          <t>1,22; 2,6</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,36</t>
+          <t>0,44; 1,4</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,61; 4,86</t>
+          <t>2,64; 4,67</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,37; 2,37</t>
+          <t>1,41; 2,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,74; 1,51</t>
+          <t>0,7; 1,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,28; 4,65</t>
+          <t>3,39; 4,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,24; 2,12</t>
+          <t>1,25; 2,12</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,8; 1,52</t>
+          <t>0,81; 1,56</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,48; 4,87</t>
+          <t>3,47; 4,97</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,42; 2,07</t>
+          <t>1,43; 2,08</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,86; 1,39</t>
+          <t>0,85; 1,38</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,62; 4,58</t>
+          <t>3,66; 4,62</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que desayuna, otros alimentos</t>
+          <t>Población que desayuna, otros alimentos (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1765; 11559</t>
+          <t>1872; 12256</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>884; 7865</t>
+          <t>881; 8025</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11673; 30343</t>
+          <t>12341; 30404</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>893; 8138</t>
+          <t>894; 9565</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3987; 16955</t>
+          <t>3393; 16838</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11207; 29446</t>
+          <t>11350; 28996</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3702; 16313</t>
+          <t>3387; 15803</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5343; 20584</t>
+          <t>5172; 19328</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>27478; 52788</t>
+          <t>27622; 52736</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4790; 18641</t>
+          <t>4509; 19418</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>993; 9278</t>
+          <t>996; 9067</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8275; 25563</t>
+          <t>8241; 25420</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2108; 11914</t>
+          <t>2347; 12580</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 11147</t>
+          <t>0; 9450</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6022; 22158</t>
+          <t>5590; 20862</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8731; 24336</t>
+          <t>9021; 25202</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2890; 14631</t>
+          <t>2777; 14849</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17576; 39734</t>
+          <t>17952; 39925</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5433; 17724</t>
+          <t>5046; 18171</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3306; 15912</t>
+          <t>3493; 14236</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13979; 32538</t>
+          <t>13883; 31421</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 6471</t>
+          <t>0; 5864</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>966; 9410</t>
+          <t>978; 9825</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1019; 11111</t>
+          <t>996; 11439</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6222; 19806</t>
+          <t>6002; 20316</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6360; 19987</t>
+          <t>6404; 20265</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17482; 38078</t>
+          <t>17164; 38006</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15722; 36777</t>
+          <t>15993; 37042</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8231; 27329</t>
+          <t>8185; 28317</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>40668; 69901</t>
+          <t>41494; 69643</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7814; 23909</t>
+          <t>8208; 24061</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4287; 17623</t>
+          <t>4623; 18746</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17659; 38013</t>
+          <t>18062; 39035</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>28971; 53191</t>
+          <t>28510; 52822</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15729; 39314</t>
+          <t>15229; 38689</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>65534; 101594</t>
+          <t>64115; 100602</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2521; 14349</t>
+          <t>2611; 14080</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>972; 9541</t>
+          <t>955; 9675</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9970; 27174</t>
+          <t>10512; 28156</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2039; 11831</t>
+          <t>2457; 11002</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2250; 12797</t>
+          <t>2197; 13358</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>31335; 58871</t>
+          <t>32451; 57766</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6427; 20418</t>
+          <t>6390; 20466</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5158; 19350</t>
+          <t>5216; 18758</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>46468; 77606</t>
+          <t>46292; 76961</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>985; 9044</t>
+          <t>989; 8290</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 6827</t>
+          <t>0; 6806</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3421; 16235</t>
+          <t>3292; 15130</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17114; 36796</t>
+          <t>17238; 36788</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4201; 17515</t>
+          <t>4091; 16891</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>28686; 54209</t>
+          <t>30576; 57225</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19499; 40701</t>
+          <t>18870; 40168</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5976; 18722</t>
+          <t>6013; 19296</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>35695; 66436</t>
+          <t>36100; 63818</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>44792; 77409</t>
+          <t>45933; 76164</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>25274; 51526</t>
+          <t>24043; 50025</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>110937; 157228</t>
+          <t>114515; 161580</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>41998; 71443</t>
+          <t>42253; 71620</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>28191; 54021</t>
+          <t>28625; 55348</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>122819; 171894</t>
+          <t>122587; 175327</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>94255; 137308</t>
+          <t>94776; 137778</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>59879; 96854</t>
+          <t>58897; 95801</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>250364; 316519</t>
+          <t>252992; 319348</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P36$otros-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P36$otros-Clase-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,59</t>
+          <t>0,4; 2,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,84</t>
+          <t>0,2; 1,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,88; 7,09</t>
+          <t>2,76; 7,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,12</t>
+          <t>0,29; 2,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 5,37</t>
+          <t>1,24; 5,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,27; 8,35</t>
+          <t>3,37; 8,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,03</t>
+          <t>0,45; 1,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,58</t>
+          <t>0,71; 2,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,56; 6,79</t>
+          <t>3,64; 7,11</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 5,32</t>
+          <t>1,4; 5,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,18</t>
+          <t>0,24; 2,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,18; 6,74</t>
+          <t>2,27; 6,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,39</t>
+          <t>0,58; 3,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,8</t>
+          <t>0,0; 3,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,51; 5,62</t>
+          <t>1,66; 5,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,42</t>
+          <t>1,19; 3,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,97</t>
+          <t>0,36; 1,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,4; 5,33</t>
+          <t>2,48; 5,63</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,36</t>
+          <t>0,95; 3,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,27</t>
+          <t>0,56; 2,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,67; 6,03</t>
+          <t>2,88; 6,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,49</t>
+          <t>0,0; 3,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,78</t>
+          <t>0,38; 3,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 6,89</t>
+          <t>0,61; 6,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,87</t>
+          <t>0,86; 2,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,28</t>
+          <t>0,66; 2,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,5; 5,53</t>
+          <t>2,42; 5,43</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,0</t>
+          <t>1,32; 2,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,45</t>
+          <t>0,74; 2,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,61; 6,06</t>
+          <t>3,52; 6,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,37</t>
+          <t>1,13; 3,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,45</t>
+          <t>0,59; 2,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,19; 4,73</t>
+          <t>2,18; 4,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,46; 2,71</t>
+          <t>1,46; 2,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,01</t>
+          <t>0,82; 2,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,25; 5,1</t>
+          <t>3,22; 5,06</t>
         </is>
       </c>
     </row>
@@ -1118,22 +1118,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,74; 4,02</t>
+          <t>0,77; 4,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,9</t>
+          <t>0,19; 1,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,7; 4,55</t>
+          <t>1,64; 4,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,94</t>
+          <t>0,34; 2,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1143,29 +1143,29 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,4; 7,82</t>
+          <t>4,24; 7,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,23</t>
+          <t>0,7; 2,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,48</t>
+          <t>0,39; 1,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,41; 5,67</t>
+          <t>3,37; 5,61</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,78</t>
+          <t>0,33; 2,41</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,55</t>
+          <t>0,0; 2,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,15; 5,27</t>
+          <t>1,18; 5,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,38; 2,95</t>
+          <t>1,4; 2,91</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,52</t>
+          <t>0,43; 1,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,83; 5,3</t>
+          <t>2,75; 5,1</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,22; 2,6</t>
+          <t>1,28; 2,66</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,4</t>
+          <t>0,44; 1,43</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,64; 4,67</t>
+          <t>2,65; 4,75</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,41; 2,33</t>
+          <t>1,37; 2,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,7; 1,46</t>
+          <t>0,72; 1,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,39; 4,78</t>
+          <t>3,38; 4,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,25; 2,12</t>
+          <t>1,25; 2,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,56</t>
+          <t>0,78; 1,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,47; 4,97</t>
+          <t>3,46; 4,86</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,43; 2,08</t>
+          <t>1,43; 2,1</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,85; 1,38</t>
+          <t>0,86; 1,41</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,66; 4,62</t>
+          <t>3,61; 4,63</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1872; 12256</t>
+          <t>1891; 12277</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>881; 8025</t>
+          <t>883; 8154</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12341; 30404</t>
+          <t>11864; 30129</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>894; 9565</t>
+          <t>893; 8386</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3393; 16838</t>
+          <t>3870; 17398</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11350; 28996</t>
+          <t>11702; 30449</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3387; 15803</t>
+          <t>3530; 15519</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5172; 19328</t>
+          <t>5366; 20550</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>27622; 52736</t>
+          <t>28280; 55171</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4509; 19418</t>
+          <t>5118; 18398</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>996; 9067</t>
+          <t>987; 9113</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8241; 25420</t>
+          <t>8549; 24692</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2347; 12580</t>
+          <t>2150; 11816</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 9450</t>
+          <t>0; 11210</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5590; 20862</t>
+          <t>6144; 22201</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9021; 25202</t>
+          <t>8746; 25400</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2777; 14849</t>
+          <t>2746; 13439</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17952; 39925</t>
+          <t>18589; 42168</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5046; 18171</t>
+          <t>5115; 18093</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3493; 14236</t>
+          <t>3542; 13875</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13883; 31421</t>
+          <t>15001; 32604</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 5864</t>
+          <t>0; 6184</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>978; 9825</t>
+          <t>979; 9880</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>996; 11439</t>
+          <t>1020; 10961</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6002; 20316</t>
+          <t>6073; 19257</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6404; 20265</t>
+          <t>5833; 19096</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17164; 38006</t>
+          <t>16650; 37296</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15993; 37042</t>
+          <t>16312; 36782</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8185; 28317</t>
+          <t>8559; 28490</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>41494; 69643</t>
+          <t>40460; 71747</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8208; 24061</t>
+          <t>8049; 23521</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4623; 18746</t>
+          <t>4508; 18857</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18062; 39035</t>
+          <t>17966; 39111</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>28510; 52822</t>
+          <t>28386; 53801</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15229; 38689</t>
+          <t>15812; 38954</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>64115; 100602</t>
+          <t>63665; 99966</t>
         </is>
       </c>
     </row>
@@ -2291,54 +2291,54 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2611; 14080</t>
+          <t>2708; 14387</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>955; 9675</t>
+          <t>961; 8782</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10512; 28156</t>
+          <t>10136; 26885</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2457; 11002</t>
+          <t>1947; 11775</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2197; 13358</t>
+          <t>2201; 13347</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>32451; 57766</t>
+          <t>31317; 57282</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6390; 20466</t>
+          <t>6440; 21327</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5216; 18758</t>
+          <t>4916; 18015</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>46292; 76961</t>
+          <t>45754; 76094</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>989; 8290</t>
+          <t>980; 7190</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 6806</t>
+          <t>0; 5825</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3292; 15130</t>
+          <t>3382; 15606</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17238; 36788</t>
+          <t>17452; 36296</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4091; 16891</t>
+          <t>4812; 17217</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>30576; 57225</t>
+          <t>29656; 55105</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18870; 40168</t>
+          <t>19849; 41191</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6013; 19296</t>
+          <t>6042; 19648</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>36100; 63818</t>
+          <t>36179; 64992</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>45933; 76164</t>
+          <t>44640; 77764</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>24043; 50025</t>
+          <t>24561; 51049</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>114515; 161580</t>
+          <t>114306; 160657</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>42253; 71620</t>
+          <t>42181; 69406</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>28625; 55348</t>
+          <t>27765; 55753</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>122587; 175327</t>
+          <t>121924; 171506</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>94776; 137778</t>
+          <t>94754; 139605</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>58897; 95801</t>
+          <t>60088; 98028</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>252992; 319348</t>
+          <t>249468; 320204</t>
         </is>
       </c>
     </row>
